--- a/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
+++ b/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
@@ -1,48 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\trans\AVLo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\trans\AVLo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8941C9EE-884F-4000-9515-E40EC5DE25A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A369826C-09F9-407B-B4B7-54AF57A8A889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="19188" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="IESS_AvgOccupancy_ROAD_RAIL_AIR" sheetId="6" r:id="rId2"/>
     <sheet name="IESS_Freight" sheetId="7" r:id="rId3"/>
     <sheet name="US_BTS NTS Modal Profile Data" sheetId="3" r:id="rId4"/>
-    <sheet name="CAN Psgr Ships" sheetId="8" r:id="rId5"/>
-    <sheet name="AVLo-passengers" sheetId="2" r:id="rId6"/>
-    <sheet name="AVLo-freight" sheetId="4" r:id="rId7"/>
+    <sheet name="SYAVLo-passengers" sheetId="9" r:id="rId5"/>
+    <sheet name="SYAVLo-freight" sheetId="10" r:id="rId6"/>
+    <sheet name="AVLo-passengers" sheetId="2" r:id="rId7"/>
+    <sheet name="AVLo-freight" sheetId="4" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="base.year">'[1]Target Year Input'!$E$3</definedName>
-    <definedName name="BTU_to_PJ">[2]Notes!$A$11</definedName>
-    <definedName name="Eno_TM" localSheetId="4">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_TM">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_Tons" localSheetId="4">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_Tons">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="MWh_to_PJ">[2]Notes!$A$12</definedName>
-    <definedName name="Sum_T2" localSheetId="4">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_T2">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_TTM" localSheetId="4">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_TTM">'[3]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="ti_tbl_50" localSheetId="4">#REF!</definedName>
+    <definedName name="base.year">#REF!</definedName>
+    <definedName name="BTU_to_PJ">#REF!</definedName>
+    <definedName name="Eno_TM">#REF!</definedName>
+    <definedName name="Eno_Tons">#REF!</definedName>
+    <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
+    <definedName name="MWh_to_PJ">#REF!</definedName>
+    <definedName name="Sum_T2">#REF!</definedName>
+    <definedName name="Sum_TTM">#REF!</definedName>
     <definedName name="ti_tbl_50">#REF!</definedName>
-    <definedName name="ti_tbl_69" localSheetId="4">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
-    <definedName name="TWh_to_PJ">[2]Notes!$A$15</definedName>
+    <definedName name="TitleRegion1.f2.y3.5">#REF!</definedName>
+    <definedName name="TitleRegion1.f3.n4.5">#REF!</definedName>
+    <definedName name="TitleRegion2.e6.y15.5">#REF!</definedName>
+    <definedName name="TitleRegion2.e8.n17.5">#REF!</definedName>
+    <definedName name="TitleRegion3.c19.y51.5">#REF!</definedName>
+    <definedName name="TitleRegion3.c24.n53.5">#REF!</definedName>
+    <definedName name="TitleRegion4.e54.y63.5">#REF!</definedName>
+    <definedName name="TitleRegion4.e57.n66.5">#REF!</definedName>
+    <definedName name="TitleRegion5.d68.y124.5">#REF!</definedName>
+    <definedName name="TitleRegion5.d73.n129.5">#REF!</definedName>
+    <definedName name="TWh_to_PJ">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="156">
   <si>
     <t>AVLo Average Vehicle Loading</t>
   </si>
@@ -124,21 +125,6 @@
     <t>Water Transport Profile</t>
   </si>
   <si>
-    <t>passenger ships</t>
-  </si>
-  <si>
-    <t>BC Ferries</t>
-  </si>
-  <si>
-    <t>Our Fleet</t>
-  </si>
-  <si>
-    <t>https://www.bcferries.com/onboard-experiences/fleet/</t>
-  </si>
-  <si>
-    <t>Numbers taken from each individual ship's webpage</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
@@ -487,135 +473,6 @@
     <t>Not currently used, but could be used instead of the figure from the National Household Travel Survey if desired.</t>
   </si>
   <si>
-    <t>Passenger Ships</t>
-  </si>
-  <si>
-    <t>Based on BC Ferries fleet</t>
-  </si>
-  <si>
-    <t>We don't have average loading levels, so we use capacities.</t>
-  </si>
-  <si>
-    <t>Ship Name</t>
-  </si>
-  <si>
-    <t>Passenger + Crew Capacity</t>
-  </si>
-  <si>
-    <t>Baynes Sound Connector</t>
-  </si>
-  <si>
-    <t>Bowen Queen</t>
-  </si>
-  <si>
-    <t>Coastal Celebration</t>
-  </si>
-  <si>
-    <t>Coastal Inspiration</t>
-  </si>
-  <si>
-    <t>Coastal Renaissance</t>
-  </si>
-  <si>
-    <t>Howe Sound Queen</t>
-  </si>
-  <si>
-    <t>Island Sky</t>
-  </si>
-  <si>
-    <t>Kahloke</t>
-  </si>
-  <si>
-    <t>Klitsa</t>
-  </si>
-  <si>
-    <t>Kuper</t>
-  </si>
-  <si>
-    <t>Kwuna</t>
-  </si>
-  <si>
-    <t>Mayne Queen</t>
-  </si>
-  <si>
-    <t>Nimpkish</t>
-  </si>
-  <si>
-    <t>North Island Princess</t>
-  </si>
-  <si>
-    <t>Northern Adventure</t>
-  </si>
-  <si>
-    <t>Northern Expedition</t>
-  </si>
-  <si>
-    <t>Powell River Queen</t>
-  </si>
-  <si>
-    <t>Quadra Queen II</t>
-  </si>
-  <si>
-    <t>Queen of Alberni</t>
-  </si>
-  <si>
-    <t>Queen of Burnaby</t>
-  </si>
-  <si>
-    <t>Queen of Capilano</t>
-  </si>
-  <si>
-    <t>Queen of Coquitlam</t>
-  </si>
-  <si>
-    <t>Queen of Cowichan</t>
-  </si>
-  <si>
-    <t>Queen of Cumberland</t>
-  </si>
-  <si>
-    <t>Queen of Nanaimo</t>
-  </si>
-  <si>
-    <t>Queen of New Westminster</t>
-  </si>
-  <si>
-    <t>Queen of Oak Bay</t>
-  </si>
-  <si>
-    <t>Queen of Surrey</t>
-  </si>
-  <si>
-    <t>Quinitsa</t>
-  </si>
-  <si>
-    <t>Quinsam</t>
-  </si>
-  <si>
-    <t>Salish Eagle</t>
-  </si>
-  <si>
-    <t>Salish Orca</t>
-  </si>
-  <si>
-    <t>Salish Raven</t>
-  </si>
-  <si>
-    <t>Skeena Queen</t>
-  </si>
-  <si>
-    <t>Spirit of British Columbia</t>
-  </si>
-  <si>
-    <t>Spirit of Vancouver Island</t>
-  </si>
-  <si>
-    <t>Tachek</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
     <t>Vehicle Loading (passengers)</t>
   </si>
   <si>
@@ -673,10 +530,10 @@
     <t>https://iess2047.gov.in/_/theme/documents/IESS2047_Version_3.0.xlsx</t>
   </si>
   <si>
-    <t>India data from IESS v3 is used for most vehicle types. US values are used for ships.</t>
-  </si>
-  <si>
     <t>Tabs XII; table 6.2 and 8.2 and XIIb; tables 6.1, 6.2 and 6.5</t>
+  </si>
+  <si>
+    <t>India data from IESS v3 is used for most vehicle types. US values are used for freight ships.</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="71">
+  <fills count="70">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1713,12 +1570,6 @@
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
         <bgColor indexed="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -3277,7 +3128,7 @@
     <xf numFmtId="0" fontId="3" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="95" fillId="69" borderId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="68" borderId="0"/>
     <xf numFmtId="169" fontId="96" fillId="61" borderId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -4067,7 +3918,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4091,18 +3942,11 @@
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="883" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4253,7 +4097,7 @@
     <xf numFmtId="181" fontId="0" fillId="62" borderId="33" xfId="579" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="62" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5829,288 +5673,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Index Page"/>
-      <sheetName val="IESS V3 Main Sheet"/>
-      <sheetName val="Data Update Sheet"/>
-      <sheetName val="Target Year Input"/>
-      <sheetName val="User-defined drivers"/>
-      <sheetName val="Control"/>
-      <sheetName val="IESS V3 Results"/>
-      <sheetName val="Intermediate output"/>
-      <sheetName val="My Story"/>
-      <sheetName val="Unit Preferences"/>
-      <sheetName val="Structure of the model"/>
-      <sheetName val="Cost - Import + Production"/>
-      <sheetName val="Cost - Power Sector and H2"/>
-      <sheetName val="Sector-wise Energy Costs"/>
-      <sheetName val="I.a"/>
-      <sheetName val="I.b"/>
-      <sheetName val="I.c"/>
-      <sheetName val="II"/>
-      <sheetName val="III"/>
-      <sheetName val="IV.a"/>
-      <sheetName val="IV.b"/>
-      <sheetName val="IV.c.1"/>
-      <sheetName val="IV.c.2"/>
-      <sheetName val="IV.d"/>
-      <sheetName val="IV.e"/>
-      <sheetName val="V.a"/>
-      <sheetName val="V.b"/>
-      <sheetName val="V.c"/>
-      <sheetName val="VI"/>
-      <sheetName val="VII.a"/>
-      <sheetName val="VII.b"/>
-      <sheetName val="VII.C"/>
-      <sheetName val="VIII"/>
-      <sheetName val="GDP"/>
-      <sheetName val="X.a"/>
-      <sheetName val="X.b"/>
-      <sheetName val="XI"/>
-      <sheetName val="XII.a"/>
-      <sheetName val="XII.b"/>
-      <sheetName val="XIII.a"/>
-      <sheetName val="XIV"/>
-      <sheetName val="XV.a"/>
-      <sheetName val="XV.b"/>
-      <sheetName val="XV.b.o"/>
-      <sheetName val="XV.c"/>
-      <sheetName val="XVI"/>
-      <sheetName val="XVII.a"/>
-      <sheetName val="XVII.b"/>
-      <sheetName val="Global assumptions"/>
-      <sheetName val="Past Data"/>
-      <sheetName val="2016-17 Static"/>
-      <sheetName val="2017-18 Static"/>
-      <sheetName val="2018-19 Static"/>
-      <sheetName val="2019-20 Static"/>
-      <sheetName val="2020-21 Static"/>
-      <sheetName val="Base Year"/>
-      <sheetName val="2022"/>
-      <sheetName val="2027"/>
-      <sheetName val="2032"/>
-      <sheetName val="2037"/>
-      <sheetName val="2042"/>
-      <sheetName val="2047"/>
-      <sheetName val="Target Year"/>
-      <sheetName val="Grid_Balance_V2"/>
-      <sheetName val="Grid balance"/>
-      <sheetName val="Conversions"/>
-      <sheetName val="Land Use"/>
-      <sheetName val="Water Use"/>
-      <sheetName val="CostAbsolute"/>
-      <sheetName val="Flows"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="3">
-          <cell r="E3">
-            <v>2020</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Notes"/>
-      <sheetName val="Comparisons"/>
-      <sheetName val="EPS Update"/>
-      <sheetName val="EPS"/>
-      <sheetName val="EIA"/>
-      <sheetName val="IESS"/>
-      <sheetName val="ICCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="11">
-          <cell r="A11">
-            <v>947817120000</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>277777.77799999999</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>3.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Rail shipments 93-97"/>
-      <sheetName val="Waterborne Flows 93-97"/>
-      <sheetName val="Air and vessel 93-97"/>
-      <sheetName val="Figure 2 compare"/>
-      <sheetName val="Factors Comparisons"/>
-      <sheetName val="1997  Table 1a Modified"/>
-      <sheetName val="Figure 1"/>
-      <sheetName val="1993-97 Table 1  US Highlights"/>
-      <sheetName val="93-97 US Freight Table 1"/>
-      <sheetName val="93-97 US Freight Table 1 (b)"/>
-      <sheetName val="93-97 Percents Tab 2&amp;3"/>
-      <sheetName val="Integrated View 93-97"/>
-      <sheetName val="Figure 3 modal shares"/>
-      <sheetName val="1993-97 Percents"/>
-      <sheetName val="BTS &amp; ORNL estimates"/>
-      <sheetName val="Oil Pipeline (2)"/>
-      <sheetName val="1997 Table 2"/>
-      <sheetName val="Table 4 Distance"/>
-      <sheetName val="Distance percent change"/>
-      <sheetName val="Distance 93-97"/>
-      <sheetName val="Distance Fig value per ton"/>
-      <sheetName val="Distance Bar"/>
-      <sheetName val="Table 5 Size 93-97"/>
-      <sheetName val="Size percent change"/>
-      <sheetName val="Size Fig value per ton"/>
-      <sheetName val="Size Bar "/>
-      <sheetName val="BTS Mode"/>
-      <sheetName val="Ton-miles data"/>
-      <sheetName val="Ton-miles figure"/>
-      <sheetName val="table 3 commodities"/>
-      <sheetName val="Commodities ranked by value"/>
-      <sheetName val="Commod ranked by tons"/>
-      <sheetName val="Commod ranked by ton-miles"/>
-      <sheetName val="Commod ranked by miles per ton "/>
-      <sheetName val="Commod ranked by val per ton"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -6398,11 +5960,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="85.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="85.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6435,12 +5997,12 @@
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>201</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6473,152 +6035,122 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="1:2">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="1:2">
       <c r="B18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="1:2">
       <c r="B19" s="2">
         <v>2016</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="1:2">
       <c r="B20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="1:2">
       <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="1:2">
       <c r="B22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="1:2">
       <c r="B23" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="1:2">
       <c r="B24" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="1:2">
       <c r="B25" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:2">
+    <row r="26" spans="1:2">
       <c r="B26" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="1:2">
       <c r="B27" s="13"/>
     </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="15" t="s">
+    <row r="28" spans="1:2">
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="2" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="2">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="2" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="2" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="B33" s="2" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="B21" r:id="rId2" location="appendix_d" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A43" r:id="rId3" xr:uid="{B413D2DC-441D-459F-B99E-302B41877040}"/>
+    <hyperlink ref="A37" r:id="rId3" xr:uid="{B413D2DC-441D-459F-B99E-302B41877040}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
@@ -6628,15 +6160,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L64"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="9" max="9" width="23.28515625" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -6645,85 +6177,86 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="45">
+      <c r="A2" s="42">
         <v>6.2</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="20"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+        <v>35</v>
+      </c>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="49">
+      <c r="A4" s="42"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="46">
         <v>2020</v>
       </c>
-      <c r="H4" s="49">
+      <c r="H4" s="46">
         <v>2022</v>
       </c>
       <c r="I4" s="1"/>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="45"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="31">
+      <c r="A5" s="42"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="28">
         <v>41.6</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="29">
         <v>41.6</v>
       </c>
-      <c r="I5" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="41">
-        <v>3</v>
+      <c r="I5" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="7">
+        <f>AVERAGE(G11:H15)</f>
+        <v>3.18</v>
       </c>
       <c r="K5" s="7">
         <f>SUM(H42:H46)</f>
@@ -6731,25 +6264,26 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="31">
+      <c r="A6" s="42"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="G6" s="28">
         <v>41.6</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="29">
         <v>41.6</v>
       </c>
       <c r="I6" t="s">
-        <v>191</v>
-      </c>
-      <c r="J6" s="41">
-        <v>3</v>
+        <v>143</v>
+      </c>
+      <c r="J6" s="7">
+        <f>AVERAGE(G21:H23)</f>
+        <v>2.6</v>
       </c>
       <c r="K6" s="7">
         <f>SUM(H52:H54)</f>
@@ -6758,108 +6292,109 @@
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="31">
+      <c r="A7" s="42"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="28">
         <v>41.6</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="29">
         <v>41.6</v>
       </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="45"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="31">
+      <c r="A8" s="42"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="28">
         <v>41.6</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="29">
         <v>41.6</v>
       </c>
       <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="45"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="33">
+      <c r="A9" s="42"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="30">
         <v>10</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="31">
         <v>10</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
+        <v>47</v>
+      </c>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="45"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="33">
+      <c r="A10" s="42"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="30">
         <v>10</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="31">
         <v>10</v>
       </c>
       <c r="I10" s="1"/>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="45"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="35">
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="32">
         <v>3.18</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="33">
         <v>3.18</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="J11" s="41">
+        <f>AVERAGE(G5:H8)</f>
+        <v>41.6</v>
       </c>
       <c r="K11" s="7">
         <f>SUM(H36:H39)</f>
@@ -6867,24 +6402,25 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="35">
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="32">
         <v>3.18</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="33">
         <v>3.18</v>
       </c>
       <c r="I12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12">
+        <v>49</v>
+      </c>
+      <c r="J12" s="38">
+        <f>AVERAGE(G9:H10)</f>
         <v>10</v>
       </c>
       <c r="K12" s="7">
@@ -6893,371 +6429,375 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="45"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="35">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="32">
         <v>3.18</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="33">
         <v>3.18</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J13">
         <f>SUMPRODUCT(J11:J12,K11:K12)/SUM(K11:K12)</f>
-        <v>40.226246020375022</v>
+        <v>40.811270136898415</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26" t="s">
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="32">
+        <v>3.18</v>
+      </c>
+      <c r="H14" s="33">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="48"/>
+      <c r="G15" s="32">
+        <v>3.18</v>
+      </c>
+      <c r="H15" s="33">
+        <v>3.18</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="35">
-        <v>3.18</v>
-      </c>
-      <c r="H14" s="36">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="35">
-        <v>3.18</v>
-      </c>
-      <c r="H15" s="36">
-        <v>3.18</v>
-      </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="37"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="41">
+        <f>AVERAGE(G26:H26)</f>
+        <v>155.16</v>
+      </c>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="29">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="23"/>
+      <c r="G18" s="32">
+        <v>1.76</v>
+      </c>
+      <c r="H18" s="33">
+        <v>1.76</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="37"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="23"/>
+      <c r="G19" s="32">
+        <v>1.76</v>
+      </c>
+      <c r="H19" s="33">
+        <v>1.76</v>
+      </c>
+      <c r="I19" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="38">
+        <f>AVERAGE(G24:H25)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="32">
+        <v>1.76</v>
+      </c>
+      <c r="H20" s="33">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="28">
+        <v>2.6</v>
+      </c>
+      <c r="H21" s="29">
+        <v>2.6</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="40"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="45"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25" t="s">
+      <c r="J21" s="37"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="28">
+        <v>2.6</v>
+      </c>
+      <c r="H22" s="29">
+        <v>2.6</v>
+      </c>
+      <c r="I22" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="41">
+        <f>AVERAGE(G16:H17)</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="23"/>
+      <c r="G23" s="28">
+        <v>2.6</v>
+      </c>
+      <c r="H23" s="29">
+        <v>2.6</v>
+      </c>
+      <c r="I23" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="41">
+        <f>AVERAGE(G18:H20)</f>
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="H16" s="32">
-        <v>1.5</v>
-      </c>
-      <c r="I16" t="s">
-        <v>57</v>
-      </c>
-      <c r="J16">
-        <v>155</v>
-      </c>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="45"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="H17" s="32">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="35">
-        <v>1.76</v>
-      </c>
-      <c r="H18" s="36">
-        <v>1.76</v>
-      </c>
-      <c r="I18" s="4" t="s">
+      <c r="D24" s="22"/>
+      <c r="E24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="30">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="31">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="41"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="G25" s="30">
+        <v>1000</v>
+      </c>
+      <c r="H25" s="31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="28">
+        <v>155.16</v>
+      </c>
+      <c r="H26" s="29">
+        <v>155.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="42"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="22"/>
+      <c r="E27" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="42"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="B29" s="49"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="50"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="51"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="52"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="51"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="52"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="51"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="52"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="40"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="45"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="35">
-        <v>1.76</v>
-      </c>
-      <c r="H19" s="36">
-        <v>1.76</v>
-      </c>
-      <c r="I19" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="45"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="35">
-        <v>1.76</v>
-      </c>
-      <c r="H20" s="36">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="45"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="31">
-        <v>2.6</v>
-      </c>
-      <c r="H21" s="32">
-        <v>2.6</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J21" s="40"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="45"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="31">
-        <v>2.6</v>
-      </c>
-      <c r="H22" s="32">
-        <v>2.6</v>
-      </c>
-      <c r="I22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J22" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="45"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="31">
-        <v>2.6</v>
-      </c>
-      <c r="H23" s="32">
-        <v>2.6</v>
-      </c>
-      <c r="I23" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="45"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="33">
-        <v>1000</v>
-      </c>
-      <c r="H24" s="34">
-        <v>1000</v>
-      </c>
-      <c r="J24" s="44"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="45"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="26"/>
-      <c r="G25" s="33">
-        <v>1000</v>
-      </c>
-      <c r="H25" s="34">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="45"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="26"/>
-      <c r="G26" s="31">
-        <v>155.16</v>
-      </c>
-      <c r="H26" s="32">
-        <v>155.16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="45"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="45"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="B29" s="52"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="53"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="54"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="55"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="54"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="55"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="54"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="55"/>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="58">
+      <c r="E35" s="54"/>
+      <c r="F35" s="55">
         <v>2020</v>
       </c>
-      <c r="G35" s="58">
+      <c r="G35" s="55">
         <v>2022</v>
       </c>
       <c r="H35" s="1">
@@ -7265,20 +6805,20 @@
       </c>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E36" s="59"/>
-      <c r="F36" s="60">
+      <c r="B36" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="56"/>
+      <c r="F36" s="57">
         <v>4672.9896115923993</v>
       </c>
-      <c r="G36" s="60">
+      <c r="G36" s="57">
         <v>4041.7216178136377</v>
       </c>
       <c r="H36" s="7">
@@ -7287,16 +6827,16 @@
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E37" s="59"/>
-      <c r="F37" s="60">
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="56"/>
+      <c r="F37" s="57">
         <v>76.115070533928943</v>
       </c>
-      <c r="G37" s="60">
+      <c r="G37" s="57">
         <v>93.423209888786772</v>
       </c>
       <c r="H37" s="7">
@@ -7305,16 +6845,16 @@
       </c>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" s="59"/>
-      <c r="F38" s="60">
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="56"/>
+      <c r="F38" s="57">
         <v>8.0872262442299494</v>
       </c>
-      <c r="G38" s="60">
+      <c r="G38" s="57">
         <v>68.899617292980238</v>
       </c>
       <c r="H38" s="7">
@@ -7323,16 +6863,16 @@
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="59"/>
-      <c r="F39" s="60">
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="56"/>
+      <c r="F39" s="57">
         <v>0</v>
       </c>
-      <c r="G39" s="60">
+      <c r="G39" s="57">
         <v>0</v>
       </c>
       <c r="H39" s="7">
@@ -7341,18 +6881,18 @@
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="25"/>
-      <c r="C40" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E40" s="59"/>
-      <c r="F40" s="60">
+      <c r="B40" s="22"/>
+      <c r="C40" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" s="56"/>
+      <c r="F40" s="57">
         <v>119.82278595144957</v>
       </c>
-      <c r="G40" s="60">
+      <c r="G40" s="57">
         <v>105.23361193967553</v>
       </c>
       <c r="H40" s="7">
@@ -7361,16 +6901,16 @@
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E41" s="59"/>
-      <c r="F41" s="60">
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="56"/>
+      <c r="F41" s="57">
         <v>1.9483379829503997</v>
       </c>
-      <c r="G41" s="60">
+      <c r="G41" s="57">
         <v>2.3916729986289895</v>
       </c>
       <c r="H41" s="7">
@@ -7379,354 +6919,354 @@
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="25"/>
-      <c r="C42" s="25" t="s">
+      <c r="B42" s="22"/>
+      <c r="C42" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" s="56"/>
+      <c r="F42" s="57">
+        <v>965.44693177152533</v>
+      </c>
+      <c r="G42" s="57">
+        <v>841.18957989395301</v>
+      </c>
+      <c r="H42" s="7">
+        <f t="shared" si="0"/>
+        <v>903.31825583273917</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" s="56"/>
+      <c r="F43" s="57">
+        <v>19.808102826662399</v>
+      </c>
+      <c r="G43" s="57">
+        <v>22.849542333169076</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="0"/>
+        <v>21.328822579915737</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="56"/>
+      <c r="F44" s="57">
+        <v>5.1501067349322236</v>
+      </c>
+      <c r="G44" s="57">
+        <v>17.300367766542301</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="0"/>
+        <v>11.225237250737262</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="56"/>
+      <c r="F45" s="57">
+        <v>0</v>
+      </c>
+      <c r="G45" s="57">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="56"/>
+      <c r="F46" s="57">
+        <v>0</v>
+      </c>
+      <c r="G46" s="57">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="22"/>
+      <c r="C47" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E42" s="59"/>
-      <c r="F42" s="60">
-        <v>965.44693177152533</v>
-      </c>
-      <c r="G42" s="60">
-        <v>841.18957989395301</v>
-      </c>
-      <c r="H42" s="7">
-        <f t="shared" si="0"/>
-        <v>903.31825583273917</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E43" s="59"/>
-      <c r="F43" s="60">
-        <v>19.808102826662399</v>
-      </c>
-      <c r="G43" s="60">
-        <v>22.849542333169076</v>
-      </c>
-      <c r="H43" s="7">
-        <f t="shared" si="0"/>
-        <v>21.328822579915737</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E44" s="59"/>
-      <c r="F44" s="60">
-        <v>5.1501067349322236</v>
-      </c>
-      <c r="G44" s="60">
-        <v>17.300367766542301</v>
-      </c>
-      <c r="H44" s="7">
-        <f t="shared" si="0"/>
-        <v>11.225237250737262</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="59"/>
-      <c r="F45" s="60">
-        <v>0</v>
-      </c>
-      <c r="G45" s="60">
-        <v>0</v>
-      </c>
-      <c r="H45" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="E46" s="59"/>
-      <c r="F46" s="60">
-        <v>0</v>
-      </c>
-      <c r="G46" s="60">
-        <v>0</v>
-      </c>
-      <c r="H46" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="25"/>
-      <c r="C47" s="25" t="s">
+      <c r="D47" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E47" s="56"/>
+      <c r="F47" s="57">
+        <v>1584.8674141560737</v>
+      </c>
+      <c r="G47" s="57">
+        <v>1357.4056846480269</v>
+      </c>
+      <c r="H47" s="7">
+        <f t="shared" si="0"/>
+        <v>1471.1365494020502</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="56"/>
+      <c r="F48" s="57">
+        <v>14.393346849046077</v>
+      </c>
+      <c r="G48" s="57">
+        <v>75.632574804435521</v>
+      </c>
+      <c r="H48" s="7">
+        <f t="shared" si="0"/>
+        <v>45.012960826740802</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="22"/>
+      <c r="C49" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" s="56"/>
+      <c r="F49" s="57">
+        <v>327.56432338353596</v>
+      </c>
+      <c r="G49" s="57">
+        <v>271.97739181447764</v>
+      </c>
+      <c r="H49" s="7">
+        <f t="shared" si="0"/>
+        <v>299.77085759900683</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="56"/>
+      <c r="F50" s="57">
+        <v>77.121711825120002</v>
+      </c>
+      <c r="G50" s="57">
+        <v>66.432204530259355</v>
+      </c>
+      <c r="H50" s="7">
+        <f t="shared" si="0"/>
+        <v>71.776958177689679</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="56"/>
+      <c r="F51" s="57">
+        <v>1.2177112393439999</v>
+      </c>
+      <c r="G51" s="57">
+        <v>16.772487282392213</v>
+      </c>
+      <c r="H51" s="7">
+        <f t="shared" si="0"/>
+        <v>8.9950992608681055</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" s="22"/>
+      <c r="C52" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="56"/>
+      <c r="F52" s="57">
+        <v>233.48395303181852</v>
+      </c>
+      <c r="G52" s="57">
+        <v>197.08614932790078</v>
+      </c>
+      <c r="H52" s="7">
+        <f t="shared" si="0"/>
+        <v>215.28505117985964</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="56"/>
+      <c r="F53" s="57">
+        <v>9.7416899147519995</v>
+      </c>
+      <c r="G53" s="57">
+        <v>8.5461619891865919</v>
+      </c>
+      <c r="H53" s="7">
+        <f t="shared" si="0"/>
+        <v>9.1439259519692957</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="56"/>
+      <c r="F54" s="57">
+        <v>0.31660492222943992</v>
+      </c>
+      <c r="G54" s="57">
+        <v>4.1371193265835089</v>
+      </c>
+      <c r="H54" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2268621244064746</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="B55" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E47" s="59"/>
-      <c r="F47" s="60">
-        <v>1584.8674141560737</v>
-      </c>
-      <c r="G47" s="60">
-        <v>1357.4056846480269</v>
-      </c>
-      <c r="H47" s="7">
-        <f t="shared" si="0"/>
-        <v>1471.1365494020502</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E48" s="59"/>
-      <c r="F48" s="60">
-        <v>14.393346849046077</v>
-      </c>
-      <c r="G48" s="60">
-        <v>75.632574804435521</v>
-      </c>
-      <c r="H48" s="7">
-        <f t="shared" si="0"/>
-        <v>45.012960826740802</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="25"/>
-      <c r="C49" s="25" t="s">
+      <c r="C55" s="22"/>
+      <c r="D55" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="56"/>
+      <c r="F55" s="57">
+        <v>424.43648146464</v>
+      </c>
+      <c r="G55" s="57">
+        <v>269.92859209439393</v>
+      </c>
+      <c r="H55" s="7">
+        <f t="shared" si="0"/>
+        <v>347.18253677951697</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="56"/>
+      <c r="F56" s="57">
+        <v>626.14886869535997</v>
+      </c>
+      <c r="G56" s="57">
+        <v>665.46751912380284</v>
+      </c>
+      <c r="H56" s="7">
+        <f t="shared" si="0"/>
+        <v>645.80819390958141</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="22"/>
+      <c r="D57" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E57" s="56"/>
+      <c r="F57" s="57">
+        <v>136.79012087999999</v>
+      </c>
+      <c r="G57" s="57">
+        <v>121.42464730316563</v>
+      </c>
+      <c r="H57" s="7">
+        <f t="shared" si="0"/>
+        <v>129.10738409158282</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" s="22"/>
+      <c r="D58" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58" s="56"/>
+      <c r="F58" s="57">
+        <v>1.8610900799999996E-3</v>
+      </c>
+      <c r="G58" s="57">
+        <v>1.5640325688888884E-3</v>
+      </c>
+      <c r="H58" s="7">
+        <f t="shared" si="0"/>
+        <v>1.712561324444444E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="56"/>
+      <c r="F59" s="57">
+        <v>7.4443603200000001E-3</v>
+      </c>
+      <c r="G59" s="57">
+        <v>6.6837954311111105E-3</v>
+      </c>
+      <c r="H59" s="7">
+        <f t="shared" si="0"/>
+        <v>7.0640778755555553E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="B60" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E49" s="59"/>
-      <c r="F49" s="60">
-        <v>327.56432338353596</v>
-      </c>
-      <c r="G49" s="60">
-        <v>271.97739181447764</v>
-      </c>
-      <c r="H49" s="7">
-        <f t="shared" si="0"/>
-        <v>299.77085759900683</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E50" s="59"/>
-      <c r="F50" s="60">
-        <v>77.121711825120002</v>
-      </c>
-      <c r="G50" s="60">
-        <v>66.432204530259355</v>
-      </c>
-      <c r="H50" s="7">
-        <f t="shared" si="0"/>
-        <v>71.776958177689679</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E51" s="59"/>
-      <c r="F51" s="60">
-        <v>1.2177112393439999</v>
-      </c>
-      <c r="G51" s="60">
-        <v>16.772487282392213</v>
-      </c>
-      <c r="H51" s="7">
-        <f t="shared" si="0"/>
-        <v>8.9950992608681055</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="25"/>
-      <c r="C52" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E52" s="59"/>
-      <c r="F52" s="60">
-        <v>233.48395303181852</v>
-      </c>
-      <c r="G52" s="60">
-        <v>197.08614932790078</v>
-      </c>
-      <c r="H52" s="7">
-        <f t="shared" si="0"/>
-        <v>215.28505117985964</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E53" s="59"/>
-      <c r="F53" s="60">
-        <v>9.7416899147519995</v>
-      </c>
-      <c r="G53" s="60">
-        <v>8.5461619891865919</v>
-      </c>
-      <c r="H53" s="7">
-        <f t="shared" si="0"/>
-        <v>9.1439259519692957</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E54" s="59"/>
-      <c r="F54" s="60">
-        <v>0.31660492222943992</v>
-      </c>
-      <c r="G54" s="60">
-        <v>4.1371193265835089</v>
-      </c>
-      <c r="H54" s="7">
-        <f t="shared" si="0"/>
-        <v>2.2268621244064746</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" s="25"/>
-      <c r="D55" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E55" s="59"/>
-      <c r="F55" s="60">
-        <v>424.43648146464</v>
-      </c>
-      <c r="G55" s="60">
-        <v>269.92859209439393</v>
-      </c>
-      <c r="H55" s="7">
-        <f t="shared" si="0"/>
-        <v>347.18253677951697</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56" s="59"/>
-      <c r="F56" s="60">
-        <v>626.14886869535997</v>
-      </c>
-      <c r="G56" s="60">
-        <v>665.46751912380284</v>
-      </c>
-      <c r="H56" s="7">
-        <f t="shared" si="0"/>
-        <v>645.80819390958141</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E57" s="59"/>
-      <c r="F57" s="60">
-        <v>136.79012087999999</v>
-      </c>
-      <c r="G57" s="60">
-        <v>121.42464730316563</v>
-      </c>
-      <c r="H57" s="7">
-        <f t="shared" si="0"/>
-        <v>129.10738409158282</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="25"/>
-      <c r="D58" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="E58" s="59"/>
-      <c r="F58" s="60">
-        <v>1.8610900799999996E-3</v>
-      </c>
-      <c r="G58" s="60">
-        <v>1.5640325688888884E-3</v>
-      </c>
-      <c r="H58" s="7">
-        <f t="shared" si="0"/>
-        <v>1.712561324444444E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="59"/>
-      <c r="F59" s="60">
-        <v>7.4443603200000001E-3</v>
-      </c>
-      <c r="G59" s="60">
-        <v>6.6837954311111105E-3</v>
-      </c>
-      <c r="H59" s="7">
-        <f t="shared" si="0"/>
-        <v>7.0640778755555553E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" s="25"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="59"/>
-      <c r="F60" s="60">
+      <c r="C60" s="22"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="57">
         <v>9305.4597054503975</v>
       </c>
-      <c r="G60" s="60">
+      <c r="G60" s="57">
         <v>8247.8279999999977</v>
       </c>
       <c r="H60" s="7">
@@ -7735,20 +7275,20 @@
       </c>
     </row>
     <row r="61" spans="2:8">
-      <c r="B61" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="25"/>
-      <c r="D61" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="59">
+      <c r="B61" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="22"/>
+      <c r="D61" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="E61" s="56">
         <v>521.23907488652435</v>
       </c>
-      <c r="F61" s="60">
+      <c r="F61" s="57">
         <v>517.73612411443764</v>
       </c>
-      <c r="G61" s="60">
+      <c r="G61" s="57">
         <v>656.29747428493329</v>
       </c>
       <c r="H61" s="7">
@@ -7757,18 +7297,18 @@
       </c>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="59">
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="56">
         <v>529.6461567395329</v>
       </c>
-      <c r="F62" s="60">
+      <c r="F62" s="57">
         <v>533.14910751161995</v>
       </c>
-      <c r="G62" s="60">
+      <c r="G62" s="57">
         <v>685.82415001963386</v>
       </c>
       <c r="H62" s="7">
@@ -7777,20 +7317,20 @@
       </c>
     </row>
     <row r="63" spans="2:8">
-      <c r="B63" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="25"/>
-      <c r="D63" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E63" s="59">
+      <c r="B63" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E63" s="56">
         <v>55.380023644905904</v>
       </c>
-      <c r="F63" s="60">
+      <c r="F63" s="57">
         <v>55.380023644905904</v>
       </c>
-      <c r="G63" s="60">
+      <c r="G63" s="57">
         <v>90.512554769095331</v>
       </c>
       <c r="H63" s="7">
@@ -7799,21 +7339,21 @@
       </c>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="63">
+      <c r="B64" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="60">
         <v>7285.73847857691</v>
       </c>
-      <c r="F64" s="64">
+      <c r="F64" s="61">
         <v>7285.7384785769109</v>
       </c>
-      <c r="G64" s="64">
+      <c r="G64" s="61">
         <v>9258.6395912346088</v>
       </c>
-      <c r="H64" s="65">
+      <c r="H64" s="62">
         <f t="shared" si="0"/>
         <v>8272.1890349057594</v>
       </c>
@@ -7827,51 +7367,50 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1">
         <v>6.5</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="B2" s="66"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="B3" s="66"/>
-      <c r="C3" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="30">
-        <f>base.year</f>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="65"/>
+      <c r="G3" s="27">
         <v>2020</v>
       </c>
-      <c r="H3" s="30">
+      <c r="H3" s="27">
         <v>2022</v>
       </c>
       <c r="I3" s="1">
@@ -7879,21 +7418,21 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="B4" s="66"/>
-      <c r="C4" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29">
+      <c r="B4" s="63"/>
+      <c r="C4" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26">
         <v>6.0999999999999979</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="26">
         <v>6.0999999999999979</v>
       </c>
       <c r="I4">
@@ -7902,17 +7441,17 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="B5" s="66"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29">
+      <c r="B5" s="63"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26">
         <v>6.0999999999999979</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="26">
         <v>6.0999999999999979</v>
       </c>
       <c r="I5">
@@ -7921,17 +7460,17 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="B6" s="66"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29">
+      <c r="B6" s="63"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26">
         <v>6.0999999999999979</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="26">
         <v>6.0999999999999979</v>
       </c>
       <c r="I6">
@@ -7940,19 +7479,19 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="B7" s="66"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29">
+      <c r="B7" s="63"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26">
         <v>1.7</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="26">
         <v>1.7</v>
       </c>
       <c r="I7">
@@ -7961,17 +7500,17 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="B8" s="66"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29">
+      <c r="B8" s="63"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26">
         <v>1.7</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="26">
         <v>1.7</v>
       </c>
       <c r="I8">
@@ -7980,17 +7519,17 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" s="66"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29">
+      <c r="B9" s="63"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26">
         <v>1.7</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="26">
         <v>1.7</v>
       </c>
       <c r="I9">
@@ -7999,19 +7538,19 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="B10" s="66"/>
-      <c r="C10" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29">
+      <c r="B10" s="63"/>
+      <c r="C10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26">
         <v>1728</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="26">
         <v>1728</v>
       </c>
       <c r="I10">
@@ -8020,17 +7559,17 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="B11" s="66"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29">
+      <c r="B11" s="63"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26">
         <v>1728</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="26">
         <v>1728</v>
       </c>
       <c r="I11">
@@ -8039,404 +7578,404 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12" s="66"/>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="63"/>
+      <c r="C12" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26">
+        <v>17.34</v>
+      </c>
+      <c r="H12" s="26">
+        <v>17.34</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>17.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.6">
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" s="68"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" s="66"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="70"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="63"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:9" ht="23.4">
+      <c r="A16" s="72">
+        <v>6</v>
+      </c>
+      <c r="B16" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29">
-        <v>17.34</v>
-      </c>
-      <c r="H12" s="29">
-        <v>17.34</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="0"/>
-        <v>17.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.75">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F13" s="71"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="69"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="66"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-    </row>
-    <row r="16" spans="1:9" ht="23.25">
-      <c r="A16" s="75">
-        <v>6</v>
-      </c>
-      <c r="B16" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="B17" s="66"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
         <v>6.1</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="B18" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="B20" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="24" t="s">
+      <c r="B20" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="76"/>
+      <c r="G20" s="27">
+        <v>2020</v>
+      </c>
+      <c r="H20" s="27">
+        <v>2022</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="0"/>
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="B21" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="79"/>
-      <c r="G20" s="30">
-        <v>2020</v>
-      </c>
-      <c r="H20" s="30">
-        <v>2022</v>
-      </c>
-      <c r="I20" s="1">
-        <f t="shared" si="0"/>
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="B21" s="25" t="s">
+      <c r="E21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="77"/>
+      <c r="G21" s="78">
+        <v>6000</v>
+      </c>
+      <c r="H21" s="79">
+        <v>6000</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="77"/>
+      <c r="G22" s="78">
+        <v>0</v>
+      </c>
+      <c r="H22" s="79">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="E23" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="80"/>
-      <c r="G21" s="81">
-        <v>6000</v>
-      </c>
-      <c r="H21" s="82">
-        <v>6000</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="80"/>
-      <c r="G22" s="81">
+      <c r="F23" s="77"/>
+      <c r="G23" s="78">
         <v>0</v>
       </c>
-      <c r="H22" s="82">
+      <c r="H23" s="79">
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="I23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="80"/>
-      <c r="G23" s="81">
+    <row r="24" spans="1:9">
+      <c r="B24" s="22"/>
+      <c r="C24" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="77"/>
+      <c r="G24" s="78">
+        <v>1180</v>
+      </c>
+      <c r="H24" s="79">
+        <v>1180</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="77"/>
+      <c r="G25" s="78">
         <v>0</v>
       </c>
-      <c r="H23" s="82">
+      <c r="H25" s="78">
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="I25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="B24" s="25"/>
-      <c r="C24" s="25" t="s">
+    <row r="26" spans="1:9">
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="77"/>
+      <c r="G26" s="78">
+        <v>0</v>
+      </c>
+      <c r="H26" s="78">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="B27" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="77"/>
+      <c r="G27" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F24" s="80"/>
-      <c r="G24" s="81">
-        <v>1180</v>
-      </c>
-      <c r="H24" s="82">
-        <v>1180</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="80"/>
-      <c r="G25" s="81">
-        <v>0</v>
-      </c>
-      <c r="H25" s="81">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="80"/>
-      <c r="G26" s="81">
-        <v>0</v>
-      </c>
-      <c r="H26" s="81">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="B27" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F27" s="80"/>
-      <c r="G27" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="82" t="s">
-        <v>73</v>
+      <c r="H27" s="79" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="80"/>
-      <c r="G28" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="82" t="s">
-        <v>73</v>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="77"/>
+      <c r="G28" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="79" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="B29" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="80"/>
-      <c r="G29" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="82" t="s">
-        <v>73</v>
+      <c r="B29" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="77"/>
+      <c r="G29" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="79" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="86"/>
-      <c r="H30" s="87"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="84"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="B31" s="66"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
         <v>6.2</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
+      <c r="B32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="22"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="24" t="s">
+      <c r="B34" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" s="76"/>
+      <c r="G34" s="27">
+        <v>2020</v>
+      </c>
+      <c r="H34" s="27">
+        <v>2022</v>
+      </c>
+      <c r="I34" s="1">
+        <f t="shared" si="0"/>
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="79"/>
-      <c r="G34" s="30">
-        <v>2020</v>
-      </c>
-      <c r="H34" s="30">
-        <v>2022</v>
-      </c>
-      <c r="I34" s="1">
-        <f t="shared" si="0"/>
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="25" t="s">
+      <c r="E35" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="80"/>
-      <c r="G35" s="81">
+      <c r="F35" s="77"/>
+      <c r="G35" s="78">
         <f t="shared" ref="G35:H40" si="1">G21+G4*10^3</f>
         <v>12099.999999999998</v>
       </c>
-      <c r="H35" s="81">
+      <c r="H35" s="78">
         <f t="shared" si="1"/>
         <v>12099.999999999998</v>
       </c>
@@ -8446,20 +7985,20 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" s="80"/>
-      <c r="G36" s="81">
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="77"/>
+      <c r="G36" s="78">
         <f t="shared" si="1"/>
         <v>6099.9999999999982</v>
       </c>
-      <c r="H36" s="81">
+      <c r="H36" s="78">
         <f t="shared" si="1"/>
         <v>6099.9999999999982</v>
       </c>
@@ -8469,20 +8008,20 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="80"/>
-      <c r="G37" s="81">
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="77"/>
+      <c r="G37" s="78">
         <f t="shared" si="1"/>
         <v>6099.9999999999982</v>
       </c>
-      <c r="H37" s="81">
+      <c r="H37" s="78">
         <f t="shared" si="1"/>
         <v>6099.9999999999982</v>
       </c>
@@ -8492,22 +8031,22 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="25"/>
-      <c r="C38" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F38" s="80"/>
-      <c r="G38" s="81">
+      <c r="B38" s="22"/>
+      <c r="C38" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="78">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="H38" s="81">
+      <c r="H38" s="78">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
@@ -8517,20 +8056,20 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" s="80"/>
-      <c r="G39" s="81">
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="78">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="H39" s="81">
+      <c r="H39" s="78">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
@@ -8540,20 +8079,20 @@
       </c>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F40" s="80"/>
-      <c r="G40" s="81">
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="77"/>
+      <c r="G40" s="78">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="H40" s="81">
+      <c r="H40" s="78">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
@@ -8563,114 +8102,114 @@
       </c>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="25"/>
-      <c r="D41" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="80"/>
-      <c r="G41" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H41" s="82" t="s">
-        <v>73</v>
+      <c r="B41" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="77"/>
+      <c r="G41" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="79" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F42" s="80"/>
-      <c r="G42" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H42" s="82" t="s">
-        <v>73</v>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="77"/>
+      <c r="G42" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="79" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" s="80"/>
-      <c r="G43" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H43" s="82" t="s">
-        <v>73</v>
+      <c r="B43" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="77"/>
+      <c r="G43" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="79" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="84"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="85"/>
-      <c r="G44" s="86"/>
-      <c r="H44" s="87"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="82"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="84"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="18">
+        <v>70</v>
+      </c>
+      <c r="D49" s="17">
         <f>I38-I24</f>
         <v>1700</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" s="18">
+      <c r="A50" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="17">
         <f>I35-I21</f>
         <v>6099.9999999999982</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="16">
+      <c r="A54" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>80</v>
-      </c>
-      <c r="D57" s="18">
-        <f>D49/A54</f>
-        <v>425</v>
+        <v>75</v>
+      </c>
+      <c r="D57" s="17">
+        <f>D49/A54/1000</f>
+        <v>0.42499999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8681,16 +8220,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C84"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="73.5703125" customWidth="1"/>
+    <col min="1" max="1" width="73.5546875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="102.28515625" customWidth="1"/>
+    <col min="3" max="3" width="102.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B1" s="4">
         <v>2006</v>
@@ -8698,7 +8237,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>8218378</v>
@@ -8706,7 +8245,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>810106273</v>
@@ -8714,7 +8253,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>39719513</v>
@@ -8722,7 +8261,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <v>7880</v>
@@ -8730,7 +8269,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>907</v>
@@ -8738,19 +8277,19 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B7" s="8">
         <f>B6/B5</f>
         <v>0.11510152284263959</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B8" s="9">
         <f>B3/(B2*(1-B7))</f>
@@ -8759,7 +8298,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B9" s="9">
         <f>B4/(B2*B7)</f>
@@ -8768,7 +8307,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B11" s="4">
         <v>2014</v>
@@ -8776,7 +8315,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B12">
         <v>15999</v>
@@ -8784,7 +8323,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B13">
         <v>339117</v>
@@ -8792,7 +8331,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B14" s="9">
         <f>B13/B12</f>
@@ -8801,7 +8340,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16" s="4">
         <v>2009</v>
@@ -8809,7 +8348,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B17">
         <v>436235</v>
@@ -8817,25 +8356,25 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B18">
         <v>1532214</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B19" s="6">
         <f>B18*10^3/B17</f>
         <v>3512.35916421195</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8845,13 +8384,13 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B21" s="4"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B22" s="11">
         <v>2009</v>
@@ -8859,7 +8398,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>38</v>
@@ -8867,7 +8406,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B24">
         <v>5914</v>
@@ -8875,7 +8414,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B25" s="6">
         <f>B24/B23</f>
@@ -8884,7 +8423,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B26" s="11">
         <v>2009</v>
@@ -8892,7 +8431,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B27" s="6">
         <v>16805</v>
@@ -8900,7 +8439,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B28" s="6">
         <v>2196</v>
@@ -8908,7 +8447,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B29" s="6">
         <v>11129</v>
@@ -8916,7 +8455,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B30" s="6">
         <v>685</v>
@@ -8924,7 +8463,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B31" s="6">
         <v>90</v>
@@ -8932,7 +8471,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B32" s="6">
         <v>337</v>
@@ -8940,7 +8479,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B33" s="6">
         <f>B27/B30</f>
@@ -8949,7 +8488,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B34" s="6">
         <f t="shared" ref="B34:B35" si="0">B28/B31</f>
@@ -8958,7 +8497,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B35" s="6">
         <f t="shared" si="0"/>
@@ -8967,7 +8506,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B36" s="6">
         <f>(B25*B24+B33*B27+B34*B28+B35*B29)/SUM(B24,B27:B29)</f>
@@ -8976,7 +8515,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B38" s="4">
         <v>2005</v>
@@ -8984,7 +8523,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B39" s="6">
         <v>2967</v>
@@ -8992,7 +8531,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B40" s="6">
         <v>100</v>
@@ -9000,35 +8539,35 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B41" s="6">
         <v>27876</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B42" s="6">
         <v>4151</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="B43" s="6"/>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B44" s="6">
         <v>6614973</v>
@@ -9036,7 +8575,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B45" s="6">
         <v>5727512</v>
@@ -9044,7 +8583,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B46" s="6">
         <v>44777151</v>
@@ -9052,7 +8591,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B47" s="6">
         <v>12172542</v>
@@ -9063,7 +8602,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B49" s="6">
         <f>B44/B39</f>
@@ -9072,7 +8611,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B50" s="6">
         <f>B45/B40</f>
@@ -9081,7 +8620,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B51" s="6">
         <f t="shared" ref="B51:B52" si="1">B46/B41</f>
@@ -9090,7 +8629,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B52" s="6">
         <f t="shared" si="1"/>
@@ -9102,7 +8641,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B54" s="6">
         <f>SUMPRODUCT(B39:B42,B49:B52)/SUM(B39:B42)</f>
@@ -9114,7 +8653,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B56" s="12">
         <v>2007</v>
@@ -9122,7 +8661,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B57">
         <v>13611</v>
@@ -9130,7 +8669,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B58">
         <v>17287</v>
@@ -9138,7 +8677,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B59" s="7">
         <f>B58/B57</f>
@@ -9150,7 +8689,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B61" s="4">
         <v>2007</v>
@@ -9158,7 +8697,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B62">
         <v>1670994</v>
@@ -9166,7 +8705,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B63" s="6">
         <v>2640170</v>
@@ -9174,14 +8713,14 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B64" s="7">
         <f>B63/B62</f>
         <v>1.579999688807979</v>
       </c>
       <c r="C64" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -9192,7 +8731,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B68" s="4">
         <v>2005</v>
@@ -9200,7 +8739,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B69" s="6">
         <v>2967</v>
@@ -9208,7 +8747,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B70" s="6">
         <v>100</v>
@@ -9216,35 +8755,35 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B71" s="6">
         <v>27876</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B72" s="6">
         <v>4151</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="B73" s="6"/>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B74" s="6">
         <v>6614973</v>
@@ -9252,7 +8791,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B75" s="6">
         <v>5727512</v>
@@ -9260,7 +8799,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B76" s="6">
         <v>44777151</v>
@@ -9268,7 +8807,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B77" s="6">
         <v>12172542</v>
@@ -9279,7 +8818,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B79" s="6">
         <f>B74/B69</f>
@@ -9288,7 +8827,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B80" s="6">
         <f>B75/B70</f>
@@ -9297,7 +8836,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B81" s="6">
         <f t="shared" ref="B81:B82" si="2">B76/B71</f>
@@ -9306,7 +8845,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B82" s="6">
         <f t="shared" si="2"/>
@@ -9318,7 +8857,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B84" s="6">
         <f>SUMPRODUCT(B69:B72,B79:B82)/SUM(B69:B72)</f>
@@ -9335,340 +8874,77 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269B9DE6-CDE0-4FF7-9473-6808F817D830}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="43.2">
+      <c r="A1" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="5">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="6">
+        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J5</f>
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="6">
+        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J11</f>
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="6">
+        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J16</f>
+        <v>155.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="6">
+        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J19</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="B6" s="6">
+        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J6</f>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B19">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B22">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B23">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B24">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>168</v>
-      </c>
-      <c r="B28">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>171</v>
-      </c>
-      <c r="B31">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>172</v>
-      </c>
-      <c r="B32">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>173</v>
-      </c>
-      <c r="B33">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>174</v>
-      </c>
-      <c r="B34">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>175</v>
-      </c>
-      <c r="B35">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>176</v>
-      </c>
-      <c r="B36">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>178</v>
-      </c>
-      <c r="B38">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>179</v>
-      </c>
-      <c r="B39">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>180</v>
-      </c>
-      <c r="B40">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>181</v>
-      </c>
-      <c r="B41">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B42" s="19">
-        <f>AVERAGE(B5:B41)</f>
-        <v>756.78378378378375</v>
+      <c r="B7" s="7">
+        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J22</f>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -9677,19 +8953,98 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F14FD45-F4B6-4457-BA24-A392C68BE721}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="43.2">
+      <c r="A1" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="9">
+        <f>IESS_Freight!D49/1000</f>
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="9">
+        <f>IESS_Freight!D50/1000</f>
+        <v>6.0999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="6">
+        <f>IESS_Freight!I12</f>
+        <v>17.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="6">
+        <f>IESS_Freight!I10</f>
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'US_BTS NTS Modal Profile Data'!B54</f>
+        <v>1974.4736422180429</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7">
+        <f>IESS_Freight!D57</f>
+        <v>0.42499999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="45">
-      <c r="A1" s="21" t="s">
-        <v>183</v>
+    <row r="1" spans="1:51" ht="43.2">
+      <c r="A1" s="18" t="s">
+        <v>135</v>
       </c>
       <c r="B1" s="1">
         <v>2021</v>
@@ -9844,622 +9199,622 @@
     </row>
     <row r="2" spans="1:51">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="B2" s="6">
         <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J5</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="C2" s="6">
         <f>B2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="D2" s="6">
         <f t="shared" ref="D2:AB2" si="0">C2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="E2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="G2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="H2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="I2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="J2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="K2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="L2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="M2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="O2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="P2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Q2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="S2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="W2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="X2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Z2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AA2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AB2" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AC2" s="6">
         <f t="shared" ref="AC2" si="1">AB2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AD2" s="6">
         <f t="shared" ref="AD2" si="2">AC2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AE2" s="6">
         <f t="shared" ref="AE2" si="3">AD2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AF2" s="6">
         <f t="shared" ref="AF2" si="4">AE2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AG2" s="6">
         <f t="shared" ref="AG2" si="5">AF2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AH2" s="6">
         <f t="shared" ref="AH2" si="6">AG2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AI2" s="6">
         <f t="shared" ref="AI2" si="7">AH2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AJ2" s="6">
         <f t="shared" ref="AJ2" si="8">AI2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AK2" s="6">
         <f t="shared" ref="AK2" si="9">AJ2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AL2" s="6">
         <f t="shared" ref="AL2" si="10">AK2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AM2" s="6">
         <f t="shared" ref="AM2" si="11">AL2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AN2" s="6">
         <f t="shared" ref="AN2" si="12">AM2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AO2" s="6">
         <f t="shared" ref="AO2" si="13">AN2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AP2" s="6">
         <f t="shared" ref="AP2" si="14">AO2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AQ2" s="6">
         <f t="shared" ref="AQ2" si="15">AP2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AR2" s="6">
         <f t="shared" ref="AR2" si="16">AQ2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AS2" s="6">
         <f t="shared" ref="AS2" si="17">AR2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AT2" s="6">
         <f t="shared" ref="AT2" si="18">AS2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AU2" s="6">
         <f t="shared" ref="AU2" si="19">AT2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AV2" s="6">
         <f t="shared" ref="AV2" si="20">AU2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AW2" s="6">
         <f t="shared" ref="AW2" si="21">AV2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AX2" s="6">
         <f t="shared" ref="AX2" si="22">AW2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AY2" s="6">
         <f t="shared" ref="AY2" si="23">AX2</f>
-        <v>3</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="3" spans="1:51">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B3" s="6">
         <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J11</f>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="C3" s="6">
         <f t="shared" ref="C3:L7" si="24">$B3</f>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="E3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="F3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="G3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="H3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="I3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="J3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="K3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="L3" s="6">
         <f t="shared" si="24"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="M3" s="6">
         <f t="shared" ref="M3:V7" si="25">$B3</f>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="N3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="T3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="U3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="V3" s="6">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="W3" s="6">
         <f t="shared" ref="W3:AL7" si="26">$B3</f>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="X3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="Y3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="Z3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AA3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AB3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AC3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AD3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AE3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AF3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AG3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AH3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AI3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AJ3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AK3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AL3" s="6">
         <f t="shared" si="26"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AM3" s="6">
-        <f t="shared" ref="AF3:AY7" si="27">$B3</f>
-        <v>41</v>
+        <f t="shared" ref="AC3:AY7" si="27">$B3</f>
+        <v>41.6</v>
       </c>
       <c r="AN3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AO3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AP3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AQ3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AR3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AS3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AT3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AU3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AV3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AW3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AX3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="AY3" s="6">
         <f t="shared" si="27"/>
-        <v>41</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="4" spans="1:51">
       <c r="A4" s="1" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="B4" s="6">
         <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J16</f>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="C4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="E4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="G4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="H4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="J4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="K4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="L4" s="6">
         <f t="shared" si="24"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="M4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="N4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="O4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="P4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="Q4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="R4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="S4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="T4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="U4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="V4" s="6">
         <f t="shared" si="25"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="W4" s="6">
         <f t="shared" si="26"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="X4" s="6">
         <f t="shared" si="26"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="Y4" s="6">
         <f t="shared" si="26"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="Z4" s="6">
         <f t="shared" si="26"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AA4" s="6">
         <f t="shared" si="26"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AB4" s="6">
         <f t="shared" si="26"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AC4" s="6">
-        <f t="shared" si="26"/>
-        <v>155</v>
+        <f t="shared" si="27"/>
+        <v>155.16</v>
       </c>
       <c r="AD4" s="6">
-        <f t="shared" si="26"/>
-        <v>155</v>
+        <f t="shared" si="27"/>
+        <v>155.16</v>
       </c>
       <c r="AE4" s="6">
-        <f t="shared" si="26"/>
-        <v>155</v>
+        <f t="shared" si="27"/>
+        <v>155.16</v>
       </c>
       <c r="AF4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AG4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AH4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AI4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AJ4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AK4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AL4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AM4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AN4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AO4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AP4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AQ4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AR4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AS4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AT4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AV4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AW4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AX4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
       <c r="AY4" s="6">
         <f t="shared" si="27"/>
-        <v>155</v>
+        <v>155.16</v>
       </c>
     </row>
     <row r="5" spans="1:51">
       <c r="A5" s="1" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="B5" s="6">
         <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J19</f>
@@ -10570,15 +9925,15 @@
         <v>1000</v>
       </c>
       <c r="AC5" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1000</v>
       </c>
       <c r="AD5" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1000</v>
       </c>
       <c r="AE5" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1000</v>
       </c>
       <c r="AF5" s="6">
@@ -10664,412 +10019,412 @@
     </row>
     <row r="6" spans="1:51">
       <c r="A6" s="1" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="B6" s="6">
         <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J6</f>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="I6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="K6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="L6" s="6">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="P6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="S6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="T6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V6" s="6">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="W6" s="6">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="X6" s="6">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" s="6">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Z6" s="6">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AA6" s="6">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AB6" s="6">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="26"/>
-        <v>3</v>
+        <f t="shared" si="27"/>
+        <v>2.6</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="26"/>
-        <v>3</v>
+        <f t="shared" si="27"/>
+        <v>2.6</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="26"/>
-        <v>3</v>
+        <f t="shared" si="27"/>
+        <v>2.6</v>
       </c>
       <c r="AF6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AG6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AI6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AJ6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AK6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AL6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AM6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AN6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AO6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AP6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AR6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AS6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AT6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AU6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AV6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AW6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AX6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AY6" s="6">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7" spans="1:51">
       <c r="A7" s="1" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="B7" s="7">
         <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J22</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="V7" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="W7" s="7">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="X7" s="7">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Y7" s="7">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" s="7">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" s="7">
-        <f t="shared" si="26"/>
-        <v>2</v>
+        <f t="shared" si="27"/>
+        <v>1.5</v>
       </c>
       <c r="AD7" s="7">
-        <f t="shared" si="26"/>
-        <v>2</v>
+        <f t="shared" si="27"/>
+        <v>1.5</v>
       </c>
       <c r="AE7" s="7">
-        <f t="shared" si="26"/>
-        <v>2</v>
+        <f t="shared" si="27"/>
+        <v>1.5</v>
       </c>
       <c r="AF7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AK7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AM7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AN7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AS7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AT7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AV7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AW7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AX7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AY7" s="7">
         <f t="shared" si="27"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -11077,20 +10432,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" ht="45">
-      <c r="A1" s="21" t="s">
-        <v>190</v>
+    <row r="1" spans="1:51" s="1" customFormat="1" ht="43.2">
+      <c r="A1" s="18" t="s">
+        <v>142</v>
       </c>
       <c r="B1" s="1">
         <v>2021</v>
@@ -11245,7 +10600,7 @@
     </row>
     <row r="2" spans="1:51">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="B2" s="9">
         <f>IESS_Freight!D49/1000</f>
@@ -11396,7 +10751,7 @@
         <v>1.7</v>
       </c>
       <c r="AM2">
-        <f t="shared" ref="AF2:AY7" si="3">$B2</f>
+        <f t="shared" ref="AM2:AY3" si="3">$B2</f>
         <v>1.7</v>
       </c>
       <c r="AN2">
@@ -11450,7 +10805,7 @@
     </row>
     <row r="3" spans="1:51">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B3" s="9">
         <f>IESS_Freight!D50/1000</f>
@@ -11573,31 +10928,31 @@
         <v>6.0999999999999979</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AL3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="AM3">
@@ -11655,7 +11010,7 @@
     </row>
     <row r="4" spans="1:51">
       <c r="A4" s="1" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="B4" s="6">
         <f>IESS_Freight!I12</f>
@@ -11770,97 +11125,97 @@
         <v>17.34</v>
       </c>
       <c r="AD4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AD4:AY7" si="4">$B4</f>
         <v>17.34</v>
       </c>
       <c r="AE4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AF4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AG4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AH4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AI4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AJ4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AK4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AL4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AM4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AN4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AO4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AP4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AQ4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AR4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AS4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AT4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AU4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AV4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AW4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AX4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
       <c r="AY4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.34</v>
       </c>
     </row>
     <row r="5" spans="1:51">
       <c r="A5" s="1" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="B5" s="6">
         <f>IESS_Freight!I10</f>
@@ -11975,97 +11330,97 @@
         <v>1728</v>
       </c>
       <c r="AD5" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AE5" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AF5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AG5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AH5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AI5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AJ5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AK5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AL5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AM5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AN5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AO5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AP5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AQ5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AR5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AS5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AT5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AU5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AV5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AW5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AX5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
       <c r="AY5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1728</v>
       </c>
     </row>
     <row r="6" spans="1:51">
       <c r="A6" s="1" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="B6" s="6">
         <f>'US_BTS NTS Modal Profile Data'!B54</f>
@@ -12180,297 +11535,297 @@
         <v>1974.4736422180429</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AI6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AJ6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AK6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AL6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AM6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AN6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AO6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AP6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AQ6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AR6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AS6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AT6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AU6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AV6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AW6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AX6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
       <c r="AY6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1974.4736422180429</v>
       </c>
     </row>
     <row r="7" spans="1:51">
       <c r="A7" s="1" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="B7">
-        <f>IESS_AvgOccupancy_ROAD_RAIL_AIR!J23</f>
-        <v>2</v>
+        <f>IESS_Freight!D57</f>
+        <v>0.42499999999999999</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="M7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="O7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="P7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="Q7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="S7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="T7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="U7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="V7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="W7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="X7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="Y7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="Z7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AA7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AB7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AC7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AL7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AM7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AN7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AO7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AP7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AQ7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AR7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AS7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AT7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AU7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AV7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AW7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AX7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="AY7">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>0.42499999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12480,6 +11835,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -12623,23 +11993,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BC38D13-C3D7-40FD-962B-206390D7AB9A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82EF9DD4-A12D-4065-A9A4-D89AC20C4B0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6EA27E2-FE52-4505-BF0D-71B6766E3316}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AE86F7E-98EB-4E98-B30C-A151F3BF0E52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -12656,19 +12028,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BC38D13-C3D7-40FD-962B-206390D7AB9A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82EF9DD4-A12D-4065-A9A4-D89AC20C4B0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>
+</clbl:labelList>
 </file>